--- a/R Markdown/resultados/tabelas_25_DA/df_reg_acoes_2025_25_DA.xlsx
+++ b/R Markdown/resultados/tabelas_25_DA/df_reg_acoes_2025_25_DA.xlsx
@@ -406,14 +406,17 @@
         </is>
       </c>
       <c r="D2">
-        <v>0</v>
+        <v>158733785.31</v>
       </c>
       <c r="E2">
-        <v>0</v>
+        <v>158733785.31</v>
       </c>
       <c r="F2">
         <v>32</v>
       </c>
+      <c r="G2">
+        <v>1</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3">
@@ -430,14 +433,17 @@
         </is>
       </c>
       <c r="D3">
-        <v>0</v>
+        <v>11001244.42</v>
       </c>
       <c r="E3">
-        <v>0</v>
+        <v>11001244.42</v>
       </c>
       <c r="F3">
         <v>5</v>
       </c>
+      <c r="G3">
+        <v>1</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4">
@@ -454,12 +460,15 @@
         </is>
       </c>
       <c r="D4">
-        <v>0</v>
+        <v>42973.15</v>
       </c>
       <c r="E4">
-        <v>0</v>
+        <v>42973.15</v>
       </c>
       <c r="F4">
+        <v>1</v>
+      </c>
+      <c r="G4">
         <v>1</v>
       </c>
     </row>
@@ -478,14 +487,17 @@
         </is>
       </c>
       <c r="D5">
-        <v>0</v>
+        <v>93558835.55</v>
       </c>
       <c r="E5">
-        <v>0</v>
+        <v>93558835.55</v>
       </c>
       <c r="F5">
         <v>21</v>
       </c>
+      <c r="G5">
+        <v>1</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6">
@@ -502,14 +514,17 @@
         </is>
       </c>
       <c r="D6">
-        <v>0</v>
+        <v>186913959.61</v>
       </c>
       <c r="E6">
-        <v>0</v>
+        <v>186913959.61</v>
       </c>
       <c r="F6">
         <v>32</v>
       </c>
+      <c r="G6">
+        <v>1</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7">
@@ -526,12 +541,15 @@
         </is>
       </c>
       <c r="D7">
-        <v>0</v>
+        <v>451115.2</v>
       </c>
       <c r="E7">
-        <v>0</v>
+        <v>451115.2</v>
       </c>
       <c r="F7">
+        <v>1</v>
+      </c>
+      <c r="G7">
         <v>1</v>
       </c>
     </row>
@@ -550,14 +568,17 @@
         </is>
       </c>
       <c r="D8">
-        <v>0</v>
+        <v>30834691.29</v>
       </c>
       <c r="E8">
-        <v>0</v>
+        <v>30834691.29</v>
       </c>
       <c r="F8">
         <v>9</v>
       </c>
+      <c r="G8">
+        <v>1</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9">
@@ -574,14 +595,17 @@
         </is>
       </c>
       <c r="D9">
-        <v>0</v>
+        <v>327248104.57</v>
       </c>
       <c r="E9">
-        <v>0</v>
+        <v>327248104.57</v>
       </c>
       <c r="F9">
         <v>22</v>
       </c>
+      <c r="G9">
+        <v>1</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10">
@@ -598,14 +622,17 @@
         </is>
       </c>
       <c r="D10">
-        <v>0</v>
+        <v>14222824.96</v>
       </c>
       <c r="E10">
-        <v>0</v>
+        <v>14222824.96</v>
       </c>
       <c r="F10">
         <v>9</v>
       </c>
+      <c r="G10">
+        <v>1</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11">
@@ -622,14 +649,17 @@
         </is>
       </c>
       <c r="D11">
-        <v>0</v>
+        <v>93869612.55</v>
       </c>
       <c r="E11">
-        <v>0</v>
+        <v>93869612.55</v>
       </c>
       <c r="F11">
         <v>8</v>
       </c>
+      <c r="G11">
+        <v>1</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12">
@@ -646,14 +676,17 @@
         </is>
       </c>
       <c r="D12">
-        <v>0</v>
+        <v>21691607.27</v>
       </c>
       <c r="E12">
-        <v>0</v>
+        <v>21691607.27</v>
       </c>
       <c r="F12">
         <v>12</v>
       </c>
+      <c r="G12">
+        <v>1</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13">
@@ -670,14 +703,17 @@
         </is>
       </c>
       <c r="D13">
-        <v>0</v>
+        <v>7296698.54</v>
       </c>
       <c r="E13">
-        <v>0</v>
+        <v>7296698.54</v>
       </c>
       <c r="F13">
         <v>21</v>
       </c>
+      <c r="G13">
+        <v>1</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14">
@@ -694,14 +730,17 @@
         </is>
       </c>
       <c r="D14">
-        <v>0</v>
+        <v>45973833.2</v>
       </c>
       <c r="E14">
-        <v>0</v>
+        <v>45973833.2</v>
       </c>
       <c r="F14">
         <v>2</v>
       </c>
+      <c r="G14">
+        <v>1</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15">
@@ -718,14 +757,17 @@
         </is>
       </c>
       <c r="D15">
-        <v>0</v>
+        <v>118693405</v>
       </c>
       <c r="E15">
-        <v>0</v>
+        <v>118693405</v>
       </c>
       <c r="F15">
         <v>35</v>
       </c>
+      <c r="G15">
+        <v>1</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16">
@@ -742,14 +784,17 @@
         </is>
       </c>
       <c r="D16">
-        <v>0</v>
+        <v>1162178834.16</v>
       </c>
       <c r="E16">
-        <v>0</v>
+        <v>1162178834.16</v>
       </c>
       <c r="F16">
         <v>21</v>
       </c>
+      <c r="G16">
+        <v>1</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17">
@@ -766,14 +811,17 @@
         </is>
       </c>
       <c r="D17">
-        <v>0</v>
+        <v>11852982.06</v>
       </c>
       <c r="E17">
-        <v>0</v>
+        <v>11852982.06</v>
       </c>
       <c r="F17">
         <v>10</v>
       </c>
+      <c r="G17">
+        <v>1</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18">
@@ -790,14 +838,17 @@
         </is>
       </c>
       <c r="D18">
-        <v>0</v>
+        <v>18652479.58</v>
       </c>
       <c r="E18">
-        <v>0</v>
+        <v>18652479.58</v>
       </c>
       <c r="F18">
         <v>7</v>
       </c>
+      <c r="G18">
+        <v>1</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19">
@@ -814,14 +865,17 @@
         </is>
       </c>
       <c r="D19">
-        <v>0</v>
+        <v>429992390.75</v>
       </c>
       <c r="E19">
-        <v>0</v>
+        <v>429992390.75</v>
       </c>
       <c r="F19">
         <v>32</v>
       </c>
+      <c r="G19">
+        <v>1</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20">
@@ -838,14 +892,17 @@
         </is>
       </c>
       <c r="D20">
-        <v>0</v>
+        <v>995502943.62</v>
       </c>
       <c r="E20">
-        <v>0</v>
+        <v>995502943.62</v>
       </c>
       <c r="F20">
         <v>5</v>
       </c>
+      <c r="G20">
+        <v>1</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21">
@@ -862,14 +919,17 @@
         </is>
       </c>
       <c r="D21">
-        <v>0</v>
+        <v>91904312.92</v>
       </c>
       <c r="E21">
-        <v>0</v>
+        <v>91904312.92</v>
       </c>
       <c r="F21">
         <v>30</v>
       </c>
+      <c r="G21">
+        <v>1</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22">
@@ -886,14 +946,17 @@
         </is>
       </c>
       <c r="D22">
-        <v>0</v>
+        <v>277357318.52</v>
       </c>
       <c r="E22">
-        <v>0</v>
+        <v>277357318.52</v>
       </c>
       <c r="F22">
         <v>31</v>
       </c>
+      <c r="G22">
+        <v>1</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23">
@@ -910,14 +973,17 @@
         </is>
       </c>
       <c r="D23">
-        <v>0</v>
+        <v>9862344.91</v>
       </c>
       <c r="E23">
-        <v>0</v>
+        <v>9862344.91</v>
       </c>
       <c r="F23">
         <v>2</v>
       </c>
+      <c r="G23">
+        <v>1</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24">
@@ -934,14 +1000,17 @@
         </is>
       </c>
       <c r="D24">
-        <v>0</v>
+        <v>43484521.34</v>
       </c>
       <c r="E24">
-        <v>0</v>
+        <v>43484521.34</v>
       </c>
       <c r="F24">
         <v>13</v>
       </c>
+      <c r="G24">
+        <v>1</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25">
@@ -958,14 +1027,17 @@
         </is>
       </c>
       <c r="D25">
-        <v>0</v>
+        <v>35456866.39</v>
       </c>
       <c r="E25">
-        <v>0</v>
+        <v>35456866.39</v>
       </c>
       <c r="F25">
         <v>3</v>
       </c>
+      <c r="G25">
+        <v>1</v>
+      </c>
     </row>
     <row r="26">
       <c r="A26">
@@ -982,14 +1054,17 @@
         </is>
       </c>
       <c r="D26">
-        <v>0</v>
+        <v>27048914.35</v>
       </c>
       <c r="E26">
-        <v>0</v>
+        <v>27048914.35</v>
       </c>
       <c r="F26">
         <v>10</v>
       </c>
+      <c r="G26">
+        <v>1</v>
+      </c>
     </row>
     <row r="27">
       <c r="A27">
@@ -1006,14 +1081,17 @@
         </is>
       </c>
       <c r="D27">
-        <v>0</v>
+        <v>96418666.62</v>
       </c>
       <c r="E27">
-        <v>0</v>
+        <v>96418666.62</v>
       </c>
       <c r="F27">
         <v>3</v>
       </c>
+      <c r="G27">
+        <v>1</v>
+      </c>
     </row>
     <row r="28">
       <c r="A28">
@@ -1030,14 +1108,17 @@
         </is>
       </c>
       <c r="D28">
-        <v>0</v>
+        <v>13419328.9</v>
       </c>
       <c r="E28">
-        <v>0</v>
+        <v>13419328.9</v>
       </c>
       <c r="F28">
         <v>11</v>
       </c>
+      <c r="G28">
+        <v>1</v>
+      </c>
     </row>
     <row r="29">
       <c r="A29">
@@ -1054,14 +1135,17 @@
         </is>
       </c>
       <c r="D29">
-        <v>0</v>
+        <v>55959202.62</v>
       </c>
       <c r="E29">
-        <v>0</v>
+        <v>55959202.62</v>
       </c>
       <c r="F29">
         <v>2</v>
       </c>
+      <c r="G29">
+        <v>1</v>
+      </c>
     </row>
     <row r="30">
       <c r="A30">
@@ -1078,14 +1162,17 @@
         </is>
       </c>
       <c r="D30">
-        <v>0</v>
+        <v>8523367.76</v>
       </c>
       <c r="E30">
-        <v>0</v>
+        <v>8523367.76</v>
       </c>
       <c r="F30">
         <v>10</v>
       </c>
+      <c r="G30">
+        <v>1</v>
+      </c>
     </row>
     <row r="31">
       <c r="A31">
@@ -1102,12 +1189,15 @@
         </is>
       </c>
       <c r="D31">
-        <v>0</v>
+        <v>135950577.37</v>
       </c>
       <c r="E31">
-        <v>0</v>
+        <v>135950577.37</v>
       </c>
       <c r="F31">
+        <v>1</v>
+      </c>
+      <c r="G31">
         <v>1</v>
       </c>
     </row>
@@ -1126,14 +1216,17 @@
         </is>
       </c>
       <c r="D32">
-        <v>0</v>
+        <v>130515638.57</v>
       </c>
       <c r="E32">
-        <v>0</v>
+        <v>130515638.57</v>
       </c>
       <c r="F32">
         <v>19</v>
       </c>
+      <c r="G32">
+        <v>1</v>
+      </c>
     </row>
     <row r="33">
       <c r="A33">
@@ -1150,14 +1243,17 @@
         </is>
       </c>
       <c r="D33">
-        <v>0</v>
+        <v>6234869.01</v>
       </c>
       <c r="E33">
-        <v>0</v>
+        <v>6234869.01</v>
       </c>
       <c r="F33">
         <v>3</v>
       </c>
+      <c r="G33">
+        <v>1</v>
+      </c>
     </row>
     <row r="34">
       <c r="A34">
@@ -1174,12 +1270,15 @@
         </is>
       </c>
       <c r="D34">
-        <v>0</v>
+        <v>103540.04</v>
       </c>
       <c r="E34">
-        <v>0</v>
+        <v>103540.04</v>
       </c>
       <c r="F34">
+        <v>1</v>
+      </c>
+      <c r="G34">
         <v>1</v>
       </c>
     </row>
@@ -1198,14 +1297,17 @@
         </is>
       </c>
       <c r="D35">
-        <v>0</v>
+        <v>48748359.48</v>
       </c>
       <c r="E35">
-        <v>0</v>
+        <v>48748359.48</v>
       </c>
       <c r="F35">
         <v>7</v>
       </c>
+      <c r="G35">
+        <v>1</v>
+      </c>
     </row>
     <row r="36">
       <c r="A36">
@@ -1222,14 +1324,17 @@
         </is>
       </c>
       <c r="D36">
-        <v>0</v>
+        <v>20294506.05</v>
       </c>
       <c r="E36">
-        <v>0</v>
+        <v>20294506.05</v>
       </c>
       <c r="F36">
         <v>12</v>
       </c>
+      <c r="G36">
+        <v>1</v>
+      </c>
     </row>
     <row r="37">
       <c r="A37">
@@ -1246,12 +1351,15 @@
         </is>
       </c>
       <c r="D37">
-        <v>0</v>
+        <v>7056576.76</v>
       </c>
       <c r="E37">
-        <v>0</v>
+        <v>7056576.76</v>
       </c>
       <c r="F37">
+        <v>1</v>
+      </c>
+      <c r="G37">
         <v>1</v>
       </c>
     </row>
@@ -1270,14 +1378,17 @@
         </is>
       </c>
       <c r="D38">
-        <v>0</v>
+        <v>2412231.29</v>
       </c>
       <c r="E38">
-        <v>0</v>
+        <v>2412231.29</v>
       </c>
       <c r="F38">
         <v>13</v>
       </c>
+      <c r="G38">
+        <v>1</v>
+      </c>
     </row>
     <row r="39">
       <c r="A39">
@@ -1294,14 +1405,17 @@
         </is>
       </c>
       <c r="D39">
-        <v>0</v>
+        <v>18975592.68</v>
       </c>
       <c r="E39">
-        <v>0</v>
+        <v>18975592.68</v>
       </c>
       <c r="F39">
         <v>13</v>
       </c>
+      <c r="G39">
+        <v>1</v>
+      </c>
     </row>
     <row r="40">
       <c r="A40">
@@ -1318,14 +1432,17 @@
         </is>
       </c>
       <c r="D40">
-        <v>0</v>
+        <v>140811.8</v>
       </c>
       <c r="E40">
-        <v>0</v>
+        <v>140811.8</v>
       </c>
       <c r="F40">
         <v>11</v>
       </c>
+      <c r="G40">
+        <v>1</v>
+      </c>
     </row>
     <row r="41">
       <c r="A41">
@@ -1342,14 +1459,17 @@
         </is>
       </c>
       <c r="D41">
-        <v>0</v>
+        <v>510000</v>
       </c>
       <c r="E41">
-        <v>0</v>
+        <v>510000</v>
       </c>
       <c r="F41">
         <v>3</v>
       </c>
+      <c r="G41">
+        <v>1</v>
+      </c>
     </row>
     <row r="42">
       <c r="A42">
@@ -1366,12 +1486,15 @@
         </is>
       </c>
       <c r="D42">
-        <v>0</v>
+        <v>416450</v>
       </c>
       <c r="E42">
-        <v>0</v>
+        <v>416450</v>
       </c>
       <c r="F42">
+        <v>1</v>
+      </c>
+      <c r="G42">
         <v>1</v>
       </c>
     </row>
@@ -1390,14 +1513,17 @@
         </is>
       </c>
       <c r="D43">
-        <v>0</v>
+        <v>5112936.54</v>
       </c>
       <c r="E43">
-        <v>0</v>
+        <v>5112936.54</v>
       </c>
       <c r="F43">
         <v>15</v>
       </c>
+      <c r="G43">
+        <v>1</v>
+      </c>
     </row>
     <row r="44">
       <c r="A44">
@@ -1414,14 +1540,17 @@
         </is>
       </c>
       <c r="D44">
-        <v>0</v>
+        <v>10643281.77</v>
       </c>
       <c r="E44">
-        <v>0</v>
+        <v>10643281.77</v>
       </c>
       <c r="F44">
         <v>16</v>
       </c>
+      <c r="G44">
+        <v>1</v>
+      </c>
     </row>
     <row r="45">
       <c r="A45">
@@ -1438,14 +1567,17 @@
         </is>
       </c>
       <c r="D45">
-        <v>0</v>
+        <v>383514285.97</v>
       </c>
       <c r="E45">
-        <v>0</v>
+        <v>383514285.97</v>
       </c>
       <c r="F45">
         <v>30</v>
       </c>
+      <c r="G45">
+        <v>1</v>
+      </c>
     </row>
     <row r="46">
       <c r="A46">
@@ -1462,14 +1594,17 @@
         </is>
       </c>
       <c r="D46">
-        <v>0</v>
+        <v>3075000</v>
       </c>
       <c r="E46">
-        <v>0</v>
+        <v>3075000</v>
       </c>
       <c r="F46">
         <v>3</v>
       </c>
+      <c r="G46">
+        <v>1</v>
+      </c>
     </row>
     <row r="47">
       <c r="A47">
@@ -1486,14 +1621,17 @@
         </is>
       </c>
       <c r="D47">
-        <v>0</v>
+        <v>381132684.59</v>
       </c>
       <c r="E47">
-        <v>0</v>
+        <v>381132684.59</v>
       </c>
       <c r="F47">
         <v>32</v>
       </c>
+      <c r="G47">
+        <v>1</v>
+      </c>
     </row>
     <row r="48">
       <c r="A48">
@@ -1510,14 +1648,17 @@
         </is>
       </c>
       <c r="D48">
-        <v>0</v>
+        <v>511078.86</v>
       </c>
       <c r="E48">
-        <v>0</v>
+        <v>511078.86</v>
       </c>
       <c r="F48">
         <v>3</v>
       </c>
+      <c r="G48">
+        <v>1</v>
+      </c>
     </row>
     <row r="49">
       <c r="A49">
@@ -1534,14 +1675,17 @@
         </is>
       </c>
       <c r="D49">
-        <v>0</v>
+        <v>718382.4400000001</v>
       </c>
       <c r="E49">
-        <v>0</v>
+        <v>718382.4400000001</v>
       </c>
       <c r="F49">
         <v>2</v>
       </c>
+      <c r="G49">
+        <v>1</v>
+      </c>
     </row>
     <row r="50">
       <c r="A50">
@@ -1558,14 +1702,17 @@
         </is>
       </c>
       <c r="D50">
-        <v>0</v>
+        <v>25813748.57</v>
       </c>
       <c r="E50">
-        <v>0</v>
+        <v>25813748.57</v>
       </c>
       <c r="F50">
         <v>4</v>
       </c>
+      <c r="G50">
+        <v>1</v>
+      </c>
     </row>
     <row r="51">
       <c r="A51">
@@ -1582,14 +1729,17 @@
         </is>
       </c>
       <c r="D51">
-        <v>0</v>
+        <v>10477847.9</v>
       </c>
       <c r="E51">
-        <v>0</v>
+        <v>10477847.9</v>
       </c>
       <c r="F51">
         <v>19</v>
       </c>
+      <c r="G51">
+        <v>1</v>
+      </c>
     </row>
     <row r="52">
       <c r="A52">
@@ -1606,14 +1756,17 @@
         </is>
       </c>
       <c r="D52">
-        <v>0</v>
+        <v>58040993.95</v>
       </c>
       <c r="E52">
-        <v>0</v>
+        <v>58040993.95</v>
       </c>
       <c r="F52">
         <v>29</v>
       </c>
+      <c r="G52">
+        <v>1</v>
+      </c>
     </row>
     <row r="53">
       <c r="A53">
@@ -1630,13 +1783,16 @@
         </is>
       </c>
       <c r="D53">
-        <v>0</v>
+        <v>21783547.49</v>
       </c>
       <c r="E53">
-        <v>0</v>
+        <v>21783547.49</v>
       </c>
       <c r="F53">
         <v>31</v>
+      </c>
+      <c r="G53">
+        <v>1</v>
       </c>
     </row>
   </sheetData>
